--- a/3d/bauteile.xlsx
+++ b/3d/bauteile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd1f7c267b9f523a/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_C5E67929C6AC4E174E89A164069789D9542CE3B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D85669F-D019-42DE-B707-7F0BE2267A36}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_C5E67929C6AC4E174E89A164069789D9542CE3B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C41F2677-C2D5-4660-AA80-EA3A89EC6F26}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="249">
   <si>
     <t>So steuerst du den 3D-Viewer</t>
   </si>
@@ -340,9 +340,6 @@
     <t>Fenster im Erdgeschoss inkl. Außenfensterbänke.</t>
   </si>
   <si>
-    <t>Rahmen</t>
-  </si>
-  <si>
     <t>Verglasung</t>
   </si>
   <si>
@@ -505,9 +502,6 @@
     <t>Hersteller</t>
   </si>
   <si>
-    <t>Vaillant</t>
-  </si>
-  <si>
     <t>haustechnik</t>
   </si>
   <si>
@@ -811,12 +805,6 @@
     <t xml:space="preserve">Holzhaus auf 250 m² · 3D-Modell </t>
   </si>
   <si>
-    <t>Kunststoff</t>
-  </si>
-  <si>
-    <t>3Fach</t>
-  </si>
-  <si>
     <t>18 KWh</t>
   </si>
   <si>
@@ -830,6 +818,36 @@
   </si>
   <si>
     <t>19,30 x 12,95 m</t>
+  </si>
+  <si>
+    <t>5,40 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaillant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">aroTHERM plus VWL 125/6 A 230V S2 </t>
+  </si>
+  <si>
+    <t>Kunststoff MD 76 PRO</t>
+  </si>
+  <si>
+    <t>Profil Fenster</t>
+  </si>
+  <si>
+    <t>3-fach Warmglas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verto S </t>
+  </si>
+  <si>
+    <t>Oberfläche</t>
+  </si>
+  <si>
+    <t>Fichte vergraut</t>
+  </si>
+  <si>
+    <t>138,5 m²</t>
   </si>
 </sst>
 </file>
@@ -1091,6 +1109,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1544,7 +1566,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1676,10 +1698,10 @@
         <v>46</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -1822,10 +1844,18 @@
       <c r="I7" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="J7" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="L7" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
@@ -1930,7 +1960,7 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>75</v>
       </c>
@@ -1957,36 +1987,36 @@
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K11" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="L11" s="5" t="s">
+      <c r="M11" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="N11" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="M11" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="O11" s="5">
         <v>0.85</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>46</v>
@@ -2002,19 +2032,19 @@
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="L12" s="5" t="s">
+      <c r="M12" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="M12" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="O12" s="5">
         <v>0.85</v>
@@ -2022,16 +2052,16 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>46</v>
@@ -2047,11 +2077,11 @@
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -2059,31 +2089,31 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -2094,17 +2124,17 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="E15" s="5" t="s">
         <v>46</v>
       </c>
@@ -2117,9 +2147,7 @@
       <c r="H15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>94</v>
-      </c>
+      <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -2129,31 +2157,31 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2164,17 +2192,17 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="E17" s="5" t="s">
         <v>46</v>
       </c>
@@ -2188,7 +2216,7 @@
         <v>46</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -2199,16 +2227,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>46</v>
@@ -2232,17 +2260,17 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="E19" s="5" t="s">
         <v>46</v>
       </c>
@@ -2253,7 +2281,7 @@
         <v>46</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
@@ -2265,17 +2293,17 @@
     </row>
     <row r="20" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="E20" s="5" t="s">
         <v>46</v>
       </c>
@@ -2286,7 +2314,7 @@
         <v>46</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
@@ -2298,17 +2326,17 @@
     </row>
     <row r="21" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>118</v>
-      </c>
       <c r="E21" s="5" t="s">
         <v>46</v>
       </c>
@@ -2319,7 +2347,7 @@
         <v>46</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
@@ -2331,17 +2359,17 @@
     </row>
     <row r="22" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="E22" s="5" t="s">
         <v>46</v>
       </c>
@@ -2352,7 +2380,7 @@
         <v>46</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
@@ -2364,17 +2392,17 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="E23" s="5" t="s">
         <v>46</v>
       </c>
@@ -2385,7 +2413,7 @@
         <v>46</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
@@ -2397,16 +2425,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>46</v>
@@ -2422,29 +2450,29 @@
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K24" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="E25" s="5" t="s">
         <v>46</v>
       </c>
@@ -2455,33 +2483,41 @@
         <v>46</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
+        <v>132</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="L25" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="M25" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="N25" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="O25" s="24" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="26" spans="1:15" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="E26" s="5" t="s">
         <v>46</v>
       </c>
@@ -2492,7 +2528,7 @@
         <v>46</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
@@ -2504,17 +2540,17 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="E27" s="5" t="s">
         <v>46</v>
       </c>
@@ -2525,7 +2561,7 @@
         <v>46</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -2537,16 +2573,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>46</v>
@@ -2562,32 +2598,32 @@
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="24" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="K28" s="24" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L28" s="24" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M28" s="24" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>46</v>
@@ -2644,28 +2680,28 @@
         <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
@@ -2673,13 +2709,13 @@
         <v>55</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="E2" s="6">
         <v>0.161</v>
@@ -2691,10 +2727,10 @@
         <v>54</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>46</v>
@@ -2702,16 +2738,16 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="5"/>
@@ -2720,7 +2756,7 @@
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>46</v>
@@ -2731,13 +2767,13 @@
         <v>47</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="E4" s="6">
         <v>0.24399999999999999</v>
@@ -2747,10 +2783,10 @@
         <v>849</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>46</v>
@@ -2761,13 +2797,13 @@
         <v>68</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E5" s="6">
         <v>0.13800000000000001</v>
@@ -2779,10 +2815,10 @@
         <v>59</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>46</v>
@@ -2790,26 +2826,26 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2839,19 +2875,19 @@
         <v>35</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2862,16 +2898,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D2" s="5">
         <v>12.5</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2882,16 +2918,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D3" s="5">
         <v>50</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2902,16 +2938,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D4" s="5">
         <v>15</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -2922,16 +2958,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D5" s="5">
         <v>200</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2942,76 +2978,76 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D6" s="5">
         <v>15</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B7" s="5">
         <v>1</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D7" s="5">
         <v>12.5</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B8" s="5">
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D8" s="5">
         <v>100</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" s="5">
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D9" s="5">
         <v>12.5</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3022,16 +3058,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" s="5">
         <v>10</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3042,16 +3078,16 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" s="5">
         <v>70</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3062,16 +3098,16 @@
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D12" s="5">
         <v>0.2</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3082,16 +3118,16 @@
         <v>4</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D13" s="5">
         <v>80</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3102,16 +3138,16 @@
         <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D14" s="5">
         <v>5</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3122,16 +3158,16 @@
         <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D15" s="5">
         <v>200</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3142,16 +3178,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D16" s="5">
         <v>0.2</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3162,16 +3198,16 @@
         <v>8</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D17" s="5">
         <v>60</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3182,16 +3218,16 @@
         <v>9</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D18" s="5">
         <v>100</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3202,16 +3238,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D19" s="5">
         <v>12.5</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3222,16 +3258,16 @@
         <v>2</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D20" s="5">
         <v>24</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3242,16 +3278,16 @@
         <v>3</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D21" s="5">
         <v>0.2</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3262,16 +3298,16 @@
         <v>4</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D22" s="5">
         <v>240</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3282,16 +3318,16 @@
         <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D23" s="5">
         <v>80</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3302,13 +3338,13 @@
         <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D24" s="5">
         <v>60</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>46</v>
@@ -3322,13 +3358,13 @@
         <v>7</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D25" s="5">
         <v>24</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>46</v>
@@ -3342,13 +3378,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D26" s="5">
         <v>0.5</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>46</v>
@@ -3362,13 +3398,13 @@
         <v>9</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D27" s="5">
         <v>30</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>46</v>
@@ -3376,62 +3412,62 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B28" s="5">
         <v>1</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D28" s="5">
         <v>15</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B29" s="5">
         <v>2</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D29" s="5">
         <v>45</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B30" s="5">
         <v>3</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D30" s="5">
         <v>160</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3463,18 +3499,18 @@
         <v>29</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>46</v>
@@ -3483,10 +3519,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>46</v>
@@ -3495,70 +3531,72 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="5"/>
+        <v>46</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>46</v>

--- a/3d/bauteile.xlsx
+++ b/3d/bauteile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd1f7c267b9f523a/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_C5E67929C6AC4E174E89A164069789D9542CE3B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C41F2677-C2D5-4660-AA80-EA3A89EC6F26}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_C5E67929C6AC4E174E89A164069789D9542CE3B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFACEA37-4633-42ED-AF1E-3F92E8199D9C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-270" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -1698,7 +1698,7 @@
         <v>46</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>111</v>
@@ -2308,7 +2308,7 @@
         <v>46</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>46</v>
@@ -2374,7 +2374,7 @@
         <v>46</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>46</v>
@@ -2407,7 +2407,7 @@
         <v>46</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>46</v>
